--- a/docs/培训/OpenWorker培训/07-租赁台账/租赁台账.xlsx
+++ b/docs/培训/OpenWorker培训/07-租赁台账/租赁台账.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46216</v>
+        <v>46221</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46144</v>
+        <v>46149</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46152</v>
+        <v>46157</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46189</v>
+        <v>46194</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46181</v>
+        <v>46186</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>46245</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>46240</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46174</v>
+        <v>46179</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46203</v>
+        <v>46208</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46182</v>
+        <v>46187</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46189</v>
+        <v>46194</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46209</v>
+        <v>46214</v>
       </c>
       <c r="H14" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>46236</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>46231</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46216</v>
+        <v>46221</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46266</v>
+        <v>46271</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46222</v>
+        <v>46227</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46266</v>
+        <v>46271</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46277</v>
+        <v>46282</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="H24" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>46272</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>46267</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46312</v>
+        <v>46317</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46319</v>
+        <v>46324</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
